--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>reward</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>##备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -1,34 +1,152 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028A3062-9E0D-47D1-AC6C-681692F893AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="questcontext" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="questcontext" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>questid</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>conditionid</t>
+  </si>
+  <si>
+    <t>nextState</t>
+  </si>
+  <si>
+    <t>reward</t>
+  </si>
+  <si>
+    <t>##备注</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int#ref=cfg.quest.TbQuest</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>list#sep=|#,int#ref=cfg.condition.TbCondition</t>
+  </si>
+  <si>
+    <t>list#sep=|#,int</t>
+  </si>
+  <si>
+    <t>list#sep=|#,list#sep=-#,int</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>唯一id</t>
+  </si>
+  <si>
+    <t>任务id</t>
+  </si>
+  <si>
+    <t>目的</t>
+  </si>
+  <si>
+    <t>完成条件</t>
+  </si>
+  <si>
+    <t>下一阶段</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
+    <t>1-500|2-1</t>
+  </si>
+  <si>
+    <t>直接上去把拳王干死！（可选）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教唆教练上去和拳王干！（可选）</t>
+  </si>
+  <si>
+    <t>被拳王打的屁滚尿流（可选）</t>
+  </si>
+  <si>
+    <t>了解现在该干什么</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2|3|4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最终节点使用负数参数标记
+-1成功
+-2失败
+跳转节点只需要填对应节点id即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +164,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,209 +476,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="4" max="4" width="27.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>questid</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>des</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>conditionid</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>nextState</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>##备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int#ref=cfg.quest.TbQuest</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>list#sep=|#,int#ref=cfg.condition.TbCondition</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>list#sep=|#,int</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>list#sep=|#,list#sep=-#,int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-1成功-2失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>唯一id</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>任务id</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>目的</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>完成条件</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>下一阶段</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>奖励</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="81" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>去找拳王对话</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1|2</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2|3</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="n">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>击败拳王</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1-500|2-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="F7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="E7" t="n">
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
+      <c r="F8" s="2">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028A3062-9E0D-47D1-AC6C-681692F893AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D673FF1A-D643-42A8-800F-37B66526CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -96,24 +96,7 @@
     <t>奖励</t>
   </si>
   <si>
-    <t>1-500|2-1</t>
-  </si>
-  <si>
-    <t>直接上去把拳王干死！（可选）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教唆教练上去和拳王干！（可选）</t>
-  </si>
-  <si>
-    <t>被拳王打的屁滚尿流（可选）</t>
-  </si>
-  <si>
     <t>了解现在该干什么</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2|3|4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -121,6 +104,33 @@
 -1成功
 -2失败
 跳转节点只需要填对应节点id即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无论怎么样让比赛开起来，让你，教练，拳王随便是谁挨顿打就行</t>
+  </si>
+  <si>
+    <t>3|4|5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">fintext </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list#sep=|#,string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成文本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你哄骗教练挨了顿打，现在比赛重启了|你挨了顿打，现在比赛重启了|拳王让你打爆了，现在比赛重启了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1|-1|-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -144,12 +154,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -164,17 +180,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -477,18 +495,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="20.75" customWidth="1"/>
     <col min="4" max="4" width="27.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.625" customWidth="1"/>
-    <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="5" max="6" width="33" customWidth="1"/>
+    <col min="7" max="7" width="29.375" customWidth="1"/>
+    <col min="8" max="8" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,17 +522,20 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -530,22 +551,26 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="81" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="81" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>29</v>
+      <c r="F3" s="3"/>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -561,14 +586,17 @@
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5">
         <v>1</v>
       </c>
@@ -576,16 +604,19 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="B6">
         <v>2</v>
       </c>
@@ -593,50 +624,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2">
-        <v>-1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E6" t="s">
         <v>26</v>
       </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2">
-        <v>-1</v>
+      <c r="F6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D673FF1A-D643-42A8-800F-37B66526CE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B286FFB9-91D8-4AD7-885B-DC0E691C8291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -94,10 +94,6 @@
   </si>
   <si>
     <t>奖励</t>
-  </si>
-  <si>
-    <t>了解现在该干什么</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>最终节点使用负数参数标记
@@ -107,13 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无论怎么样让比赛开起来，让你，教练，拳王随便是谁挨顿打就行</t>
-  </si>
-  <si>
-    <t>3|4|5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">fintext </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -131,6 +120,21 @@
   </si>
   <si>
     <t>-1|-1|-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2|3|4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问问教练现在该干什么</t>
+  </si>
+  <si>
+    <t>问问教练现在该干什么</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无论怎么样让比赛开起来，让你，教练，拳王随便是谁&lt;color=red&gt;挨顿打&lt;/color&gt;就行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -523,7 +527,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -552,7 +556,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -561,13 +565,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.15">
@@ -587,7 +591,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
@@ -604,19 +608,19 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="B6">
         <v>2</v>
       </c>
@@ -624,16 +628,16 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/questcontext.xlsx
+++ b/DataTables/Datas/questcontext.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B286FFB9-91D8-4AD7-885B-DC0E691C8291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F58D0D0-8128-4672-9401-3AB534A4A93B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -115,18 +115,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>你哄骗教练挨了顿打，现在比赛重启了|你挨了顿打，现在比赛重启了|拳王让你打爆了，现在比赛重启了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-1|-1|-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2|3|4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>问问教练现在该干什么</t>
   </si>
   <si>
@@ -135,6 +123,26 @@
   </si>
   <si>
     <t>无论怎么样让比赛开起来，让你，教练，拳王随便是谁&lt;color=red&gt;挨顿打&lt;/color&gt;就行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12|3|4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练心中燃起了火，他要好好教训拳王一下|你挨了顿打，现在比赛重启了|拳王让你打爆了，现在比赛重启了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观赏一下这场伟大的比赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教练这下彻底让拳王打瘪了，真没出息，不过好歹拳赛开起来了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3|-1|-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -608,13 +616,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -628,16 +636,36 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>28</v>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
